--- a/attendance_list.xlsx
+++ b/attendance_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,31 @@
           <t>19-04-2026 | 02:36</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>04-05-2026 | 20:49</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>12-05-2026 | 20:58</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>12-05-2026 | 21:13</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>12-05-2026 | 21:34</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>12-05-2026 | 22:16</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -519,6 +544,31 @@
           <t>❌ Absent</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>✅ Present (20:49:24)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>❌ Absent</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>❌ Absent</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>❌ Absent</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>❌ Absent</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -569,6 +619,262 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>✅ Present (02:37:26)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>✅ Present (20:49:20)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>❌ Absent</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>❌ Absent</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>❌ Absent</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>❌ Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>22050111069</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>berat mut</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>✅ Present (20:58:38)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>✅ Present (21:13:37)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>✅ Present (21:34:13)</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>✅ Present (22:17:03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>22050111046</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>cüneyt şahin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>❌ Absent</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>❌ Absent</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>❌ Absent</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>❌ Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>22050111099</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ömer ersin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>✅ Present (22:17:00)</t>
         </is>
       </c>
     </row>

--- a/attendance_list.xlsx
+++ b/attendance_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,67 +429,47 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>19-04-2026 | 00:52</t>
+          <t>13-05-2026 | 16:33</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>19-04-2026 | 01:28</t>
+          <t>13-05-2026 | 16:41</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>19-04-2026 | 01:29</t>
+          <t>13-05-2026 | 16:51</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>19-04-2026 | 01:38</t>
+          <t>13-05-2026 | 16:52</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>19-04-2026 | 02:07</t>
+          <t>13-05-2026 | 18:50</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>19-04-2026 | 02:15</t>
+          <t>13-05-2026 | 18:51</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>19-04-2026 | 02:26</t>
+          <t>13-05-2026 | 18:52</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>19-04-2026 | 02:36</t>
+          <t>13-05-2026 | 18:54</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>04-05-2026 | 20:49</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>12-05-2026 | 20:58</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>12-05-2026 | 21:13</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>12-05-2026 | 21:34</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>12-05-2026 | 22:16</t>
+          <t>13-05-2026 | 18:55</t>
         </is>
       </c>
     </row>
@@ -511,17 +491,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>❌ Absent</t>
+          <t>✅ Present (16:41:45)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>❌ Absent</t>
+          <t>✅ Present (16:51:34)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>✅ Present (01:38:13)</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -531,12 +511,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>❌ Absent</t>
+          <t>✅ Present (18:51:12)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>✅ Present (02:26:53)</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -545,26 +525,6 @@
         </is>
       </c>
       <c r="K2" t="inlineStr">
-        <is>
-          <t>✅ Present (20:49:24)</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>❌ Absent</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>❌ Absent</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>❌ Absent</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
         <is>
           <t>❌ Absent</t>
         </is>
@@ -573,17 +533,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22050111045</t>
+          <t>22050111069</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>celal sengör</t>
+          <t>berat mut</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>❌ Absent</t>
+          <t>✅ Present (16:33:49)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -598,50 +558,30 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>✅ Present (01:38:10)</t>
+          <t>✅ Present (16:52:14)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>❌ Absent</t>
+          <t>✅ Present (18:50:29)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>❌ Absent</t>
+          <t>✅ Present (18:51:39)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>✅ Present (02:26:50)</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>✅ Present (02:37:26)</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
-        <is>
-          <t>✅ Present (20:49:20)</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>❌ Absent</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>❌ Absent</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>❌ Absent</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
         <is>
           <t>❌ Absent</t>
         </is>
@@ -650,152 +590,112 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22050111069</t>
+          <t>22050111046</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>berat mut</t>
+          <t>cüneyt şahin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>✅ Present (18:54:53)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>✅ Present (20:58:38)</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>✅ Present (21:13:37)</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>✅ Present (21:34:13)</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>✅ Present (22:17:03)</t>
+          <t>❌ Absent</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22050111046</t>
+          <t>22050111099</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cüneyt şahin</t>
+          <t>ömer ersin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>✅ Present (16:33:47)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>✅ Present (16:52:11)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>✅ Present (18:50:26)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>✅ Present (18:51:37)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>❌ Absent</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>❌ Absent</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>❌ Absent</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
         <is>
           <t>❌ Absent</t>
         </is>
@@ -804,77 +704,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22050111099</t>
+          <t>22050111043</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ömer ersin</t>
+          <t>celal şengör</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>✅ Present (16:41:42)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>✅ Present (16:51:31)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>✅ Present (18:51:09)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>❌ Absent</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>✅ Present (22:17:00)</t>
+          <t>❌ Absent</t>
         </is>
       </c>
     </row>
